--- a/data/xlsx/CL.xlsx
+++ b/data/xlsx/CL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mark/sites/codeforiati/gov-id-finder-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C91C9FC-B27E-5443-B4FA-9D9F3ED8670F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079E9601-E672-174C-AA5B-962EDAD00C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{629A7C42-3E54-6C41-947C-FC27A6453A99}"/>
   </bookViews>
@@ -57,9 +57,6 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
     <t>Branch / Sector</t>
   </si>
   <si>
@@ -526,6 +523,9 @@
   </si>
   <si>
     <t>name_en</t>
+  </si>
+  <si>
+    <t>code</t>
   </si>
 </sst>
 </file>
@@ -570,9 +570,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
@@ -614,13 +613,13 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{B6C370B9-C230-E449-AF18-389A5F654EFD}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="6">
+  <queryTableRefresh nextId="8">
     <queryTableFields count="5">
+      <queryTableField id="2" name="Code" tableColumnId="2"/>
+      <queryTableField id="4" name="Name (English)" tableColumnId="4"/>
+      <queryTableField id="3" name="Name (Spanish)" tableColumnId="3"/>
+      <queryTableField id="5" name="Branch / Sector" tableColumnId="5"/>
       <queryTableField id="1" name="Identifier" tableColumnId="1"/>
-      <queryTableField id="2" name="Code" tableColumnId="2"/>
-      <queryTableField id="3" name="Name (Spanish)" tableColumnId="3"/>
-      <queryTableField id="4" name="Name (English)" tableColumnId="4"/>
-      <queryTableField id="5" name="Branch / Sector" tableColumnId="5"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -641,11 +640,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2042D231-369B-D142-86E8-3B9A583C48AC}" name="CL_COA" displayName="CL_COA" ref="A1:E34" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:E34" xr:uid="{2042D231-369B-D142-86E8-3B9A583C48AC}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8C7825CB-C673-554E-9CB7-D68251BAF9AD}" uniqueName="1" name="Identifier" queryTableFieldId="1" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{4B923001-E932-B648-B3CF-7BD5AAC05B4C}" uniqueName="2" name="Code" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{0DE73B99-6E8A-4345-B669-618C5AEA39C1}" uniqueName="3" name="name_es" queryTableFieldId="3" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{4FC33DE8-0599-6640-9D9F-FB71207CBCDB}" uniqueName="4" name="name_en" queryTableFieldId="4" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{32824CFB-6F88-9D4F-8772-5C5539E1CACF}" uniqueName="5" name="Branch / Sector" queryTableFieldId="5" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{4B923001-E932-B648-B3CF-7BD5AAC05B4C}" uniqueName="2" name="code" queryTableFieldId="2"/>
+    <tableColumn id="4" xr3:uid="{4FC33DE8-0599-6640-9D9F-FB71207CBCDB}" uniqueName="4" name="name_en" queryTableFieldId="4" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{0DE73B99-6E8A-4345-B669-618C5AEA39C1}" uniqueName="3" name="name_es" queryTableFieldId="3" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{32824CFB-6F88-9D4F-8772-5C5539E1CACF}" uniqueName="5" name="Branch / Sector" queryTableFieldId="5" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{8C7825CB-C673-554E-9CB7-D68251BAF9AD}" uniqueName="1" name="Identifier" queryTableFieldId="1" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -655,8 +654,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D698443C-FD8F-0346-9047-A1E7B036DA3B}" name="CL_COA_meta" displayName="CL_COA_meta" ref="A1:B20" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:B20" xr:uid="{D698443C-FD8F-0346-9047-A1E7B036DA3B}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{024A5528-5605-564E-BC50-CFA389486FCA}" uniqueName="1" name="Column1" queryTableFieldId="1" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{CA9F10D0-2B18-BF43-B579-88D13B31C558}" uniqueName="2" name="Column2" queryTableFieldId="2" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{024A5528-5605-564E-BC50-CFA389486FCA}" uniqueName="1" name="Column1" queryTableFieldId="1" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{CA9F10D0-2B18-BF43-B579-88D13B31C558}" uniqueName="2" name="Column2" queryTableFieldId="2" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -982,589 +981,589 @@
   <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" customWidth="1"/>
+    <col min="5" max="5" width="49" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
+      <c r="E2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
+      <c r="E3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>6</v>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>20</v>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>20</v>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>20</v>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="B32" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14">
-        <v>13</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15">
-        <v>14</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16">
-        <v>15</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="B33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34">
         <v>50</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17">
-        <v>16</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18">
-        <v>17</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19">
-        <v>18</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20">
-        <v>19</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21">
-        <v>20</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22">
-        <v>21</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23">
-        <v>22</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24">
-        <v>23</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25">
-        <v>24</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26">
-        <v>25</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B27">
-        <v>26</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28">
-        <v>27</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29">
-        <v>28</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30">
-        <v>29</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31">
-        <v>30</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32">
-        <v>31</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B33">
-        <v>32</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="B34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" t="s">
         <v>102</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34">
-        <v>50</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1586,162 +1585,162 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" t="s">
         <v>107</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="B2" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="B3" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="B4" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="B5" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="B6" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="B7" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="B8" t="s">
         <v>121</v>
       </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="B9" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="3" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="B11" t="s">
         <v>127</v>
       </c>
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="B12" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="1" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="B13" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+      <c r="B14" t="s">
         <v>133</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="B15" t="s">
         <v>135</v>
       </c>
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="B16" t="s">
         <v>137</v>
       </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="B17" t="s">
         <v>139</v>
       </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="B18" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+      <c r="B19" t="s">
         <v>143</v>
       </c>
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="B20" t="s">
         <v>145</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>
